--- a/data/bank-2026.xlsx
+++ b/data/bank-2026.xlsx
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_ALFA по карте VISA 4274259C13708840 за 2026-01-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_896126 Чек он-лайн №469251 от 03.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_ALFA по карте VISA 4274120034567890 за 2026-01-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_896126 Чек он-лайн №469251 от 03.01.2026</t>
         </is>
       </c>
       <c r="D2" s="9" t="n"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_ALFA по карте VISA 4274259C13708840 за 2026-01-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_977395 Чек он-лайн №406785 от 03.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_ALFA по карте VISA 4274120034567890 за 2026-01-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_977395 Чек он-лайн №406785 от 03.01.2026</t>
         </is>
       </c>
       <c r="D3" s="9" t="n"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274259C13708840 за 2026-01-08. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_110362 Чек он-лайн №601146 от 08.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274120034567890 за 2026-01-08. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_110362 Чек он-лайн №601146 от 08.01.2026</t>
         </is>
       </c>
       <c r="D4" s="9" t="n"/>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-01-11. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_593931 Чек он-лайн №708781 от 11.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-01-11. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_593931 Чек он-лайн №708781 от 11.01.2026</t>
         </is>
       </c>
       <c r="D5" s="9" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_ALFA по карте VISA 4274259C13708840 за 2026-01-14. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_210972 Чек он-лайн №532039 от 14.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_ALFA по карте VISA 4274120034567890 за 2026-01-14. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_210972 Чек он-лайн №532039 от 14.01.2026</t>
         </is>
       </c>
       <c r="D6" s="9" t="n"/>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-01-15. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_253899 Чек он-лайн №149405 от 15.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-01-15. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_253899 Чек он-лайн №149405 от 15.01.2026</t>
         </is>
       </c>
       <c r="D7" s="9" t="n"/>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ONLAYN_MARKET по карте VISA 4274259C13708840 за 2026-01-17. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_782323 Чек он-лайн №205406 от 17.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ONLAYN_MARKET по карте VISA 4274120034567890 за 2026-01-17. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_782323 Чек он-лайн №205406 от 17.01.2026</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка PROFESSIONAL. по карте VISA 4274259C13708840 за 2026-01-17. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_002193 Чек он-лайн №902924 от 17.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф PROFESSIONAL. по карте VISA 4274120034567890 за 2026-01-17. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_002193 Чек он-лайн №902924 от 17.01.2026</t>
         </is>
       </c>
       <c r="D9" s="9" t="n"/>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274259C13708840 за 2026-01-17. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_230696 Чек он-лайн №591350 от 17.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274120034567890 за 2026-01-17. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_230696 Чек он-лайн №591350 от 17.01.2026</t>
         </is>
       </c>
       <c r="D10" s="9" t="n"/>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-01-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_967073 Чек он-лайн №587282 от 19.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-01-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_967073 Чек он-лайн №587282 от 19.01.2026</t>
         </is>
       </c>
       <c r="D11" s="9" t="n"/>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_BETA по карте VISA 4274259C13708840 за 2026-01-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_825639 Чек он-лайн №885248 от 19.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_BETA по карте VISA 4274120034567890 за 2026-01-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_825639 Чек он-лайн №885248 от 19.01.2026</t>
         </is>
       </c>
       <c r="D12" s="9" t="n"/>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ HOSTING_SERVIS по карте VISA 4274259C13708840 за 2026-01-21. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1110 КА_643675 Чек он-лайн №584167 от 21.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ HOSTING_SERVIS по карте VISA 4274120034567890 за 2026-01-21. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1110 КА_643675 Чек он-лайн №584167 от 21.01.2026</t>
         </is>
       </c>
       <c r="D13" s="9" t="n"/>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-01-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_753850 Чек он-лайн №521318 от 22.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-01-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_753850 Чек он-лайн №521318 от 22.01.2026</t>
         </is>
       </c>
       <c r="D14" s="9" t="n"/>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-01-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_435991 Чек он-лайн №199565 от 22.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-01-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_435991 Чек он-лайн №199565 от 22.01.2026</t>
         </is>
       </c>
       <c r="D15" s="9" t="n"/>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_EPSILON по карте VISA 4274259C13708840 за 2026-01-23. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_578053 Чек он-лайн №740137 от 23.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_EPSILON по карте VISA 4274120034567890 за 2026-01-23. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_578053 Чек он-лайн №740137 от 23.01.2026</t>
         </is>
       </c>
       <c r="D16" s="9" t="n"/>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-01-25. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_585455 Чек он-лайн №702556 от 25.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-01-25. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_585455 Чек он-лайн №702556 от 25.01.2026</t>
         </is>
       </c>
       <c r="D17" s="9" t="n"/>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка WB*ONLAYN_MARKET по карте VISA 4274259C13708840 за 2026-01-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_631311 Чек он-лайн №461285 от 26.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф WB*ONLAYN_MARKET по карте VISA 4274120034567890 за 2026-01-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_631311 Чек он-лайн №461285 от 26.01.2026</t>
         </is>
       </c>
       <c r="D18" s="9" t="n"/>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-01-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_172338 Чек он-лайн №749199 от 26.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-01-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_172338 Чек он-лайн №749199 от 26.01.2026</t>
         </is>
       </c>
       <c r="D19" s="9" t="n"/>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-01-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_799673 Чек он-лайн №233005 от 27.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-01-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_799673 Чек он-лайн №233005 от 27.01.2026</t>
         </is>
       </c>
       <c r="D20" s="9" t="n"/>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ OBLAKO_SERVIS по карте VISA 4274259C13708840 за 2026-01-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_692051 Чек он-лайн №921945 от 29.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ OBLAKO_SERVIS по карте VISA 4274120034567890 за 2026-01-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_692051 Чек он-лайн №921945 от 29.01.2026</t>
         </is>
       </c>
       <c r="D21" s="9" t="n"/>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ AZS 1 по карте VISA 4274259C13708840 за 2026-01-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_244597 Чек он-лайн №473657 от 29.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ AZS 1 по карте VISA 4274120034567890 за 2026-01-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_244597 Чек он-лайн №473657 от 29.01.2026</t>
         </is>
       </c>
       <c r="D22" s="9" t="n"/>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_DZETA по карте VISA 4274259C13708840 за 2026-01-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_275956 Чек он-лайн №205427 от 29.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_DZETA по карте VISA 4274120034567890 за 2026-01-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_275956 Чек он-лайн №205427 от 29.01.2026</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ONLAYN_PLATFORMA по карте VISA 4274259C13708840 за 2026-01-30. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_141327 Чек он-лайн №907672 от 30.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ONLAYN_PLATFORMA по карте VISA 4274120034567890 за 2026-01-30. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_141327 Чек он-лайн №907672 от 30.01.2026</t>
         </is>
       </c>
       <c r="D24" s="9" t="n"/>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-01-30. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_892065 Чек он-лайн №773306 от 30.01.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-01-30. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_892065 Чек он-лайн №773306 от 30.01.2026</t>
         </is>
       </c>
       <c r="D25" s="9" t="n"/>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_504665 Чек он-лайн №408572 от 01.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_504665 Чек он-лайн №408572 от 01.02.2026</t>
         </is>
       </c>
       <c r="D26" s="9" t="n"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_422027 Чек он-лайн №533665 от 01.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_422027 Чек он-лайн №533665 от 01.02.2026</t>
         </is>
       </c>
       <c r="D27" s="9" t="n"/>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Petrozavodsk-Lada по карте VISA 4274259C13708840 за 2026-02-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_624603 Чек он-лайн №659187 от 01.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Petrozavodsk-Lada по карте VISA 4274120034567890 за 2026-02-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_624603 Чек он-лайн №659187 от 01.02.2026</t>
         </is>
       </c>
       <c r="D28" s="9" t="n"/>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_561106 Чек он-лайн №709708 от 02.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_561106 Чек он-лайн №709708 от 02.02.2026</t>
         </is>
       </c>
       <c r="D29" s="9" t="n"/>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274259C13708840 за 2026-02-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_342280 Чек он-лайн №238696 от 05.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274120034567890 за 2026-02-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_342280 Чек он-лайн №238696 от 05.02.2026</t>
         </is>
       </c>
       <c r="D30" s="9" t="n"/>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274259C13708840 за 2026-02-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_636004 Чек он-лайн №712573 от 05.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274120034567890 за 2026-02-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_636004 Чек он-лайн №712573 от 05.02.2026</t>
         </is>
       </c>
       <c r="D31" s="9" t="n"/>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274259C13708840 за 2026-02-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_171507 Чек он-лайн №781668 от 05.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274120034567890 за 2026-02-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_171507 Чек он-лайн №781668 от 05.02.2026</t>
         </is>
       </c>
       <c r="D32" s="9" t="n"/>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274259C13708840 за 2026-02-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_766636 Чек он-лайн №374737 от 05.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274120034567890 за 2026-02-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_766636 Чек он-лайн №374737 от 05.02.2026</t>
         </is>
       </c>
       <c r="D33" s="9" t="n"/>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_986450 Чек он-лайн №292565 от 05.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_986450 Чек он-лайн №292565 от 05.02.2026</t>
         </is>
       </c>
       <c r="D34" s="9" t="n"/>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-06. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_925463 Чек он-лайн №917687 от 06.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-06. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_925463 Чек он-лайн №917687 от 06.02.2026</t>
         </is>
       </c>
       <c r="D35" s="9" t="n"/>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_2 по карте VISA 4274259C13708840 за 2026-02-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_805682 Чек он-лайн №928360 от 09.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_2 по карте VISA 4274120034567890 за 2026-02-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_805682 Чек он-лайн №928360 от 09.02.2026</t>
         </is>
       </c>
       <c r="D36" s="9" t="n"/>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка MAGNIT MK MENERGO_SERVISA по карте VISA 4274259C13708840 за 2026-02-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_227014 Чек он-лайн №726958 от 09.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф MAGNIT MK MENERGO_SERVISA по карте VISA 4274120034567890 за 2026-02-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_227014 Чек он-лайн №726958 от 09.02.2026</t>
         </is>
       </c>
       <c r="D37" s="9" t="n"/>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KUZNETSOVA M.A. по карте VISA 4274259C13708840 за 2026-02-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_375965 Чек он-лайн №514931 от 09.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KUZNETSOVA M.A. по карте VISA 4274120034567890 за 2026-02-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_375965 Чек он-лайн №514931 от 09.02.2026</t>
         </is>
       </c>
       <c r="D38" s="9" t="n"/>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ONLAYN_PLATFORMA по карте VISA 4274259C13708840 за 2026-02-10. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_606894 Чек он-лайн №928261 от 10.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ONLAYN_PLATFORMA по карте VISA 4274120034567890 за 2026-02-10. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_606894 Чек он-лайн №928261 от 10.02.2026</t>
         </is>
       </c>
       <c r="D39" s="9" t="n"/>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-11. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_733701 Чек он-лайн №611309 от 11.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-11. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_733701 Чек он-лайн №611309 от 11.02.2026</t>
         </is>
       </c>
       <c r="D40" s="9" t="n"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-11. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_314006 Чек он-лайн №805654 от 11.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-11. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_314006 Чек он-лайн №805654 от 11.02.2026</t>
         </is>
       </c>
       <c r="D41" s="9" t="n"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KUZNETSOVA M.A. по карте VISA 4274259C13708840 за 2026-02-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_726746 Чек он-лайн №468559 от 13.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KUZNETSOVA M.A. по карте VISA 4274120034567890 за 2026-02-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_726746 Чек он-лайн №468559 от 13.02.2026</t>
         </is>
       </c>
       <c r="D42" s="9" t="n"/>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_240913 Чек он-лайн №204070 от 13.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_240913 Чек он-лайн №204070 от 13.02.2026</t>
         </is>
       </c>
       <c r="D43" s="9" t="n"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_428368 Чек он-лайн №837969 от 13.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_428368 Чек он-лайн №837969 от 13.02.2026</t>
         </is>
       </c>
       <c r="D44" s="9" t="n"/>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_ETA по карте VISA 4274259C13708840 за 2026-02-14. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_135072 Чек он-лайн №830818 от 14.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_ETA по карте VISA 4274120034567890 за 2026-02-14. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_135072 Чек он-лайн №830818 от 14.02.2026</t>
         </is>
       </c>
       <c r="D45" s="9" t="n"/>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_896503 Чек он-лайн №830007 от 16.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_896503 Чек он-лайн №830007 от 16.02.2026</t>
         </is>
       </c>
       <c r="D46" s="9" t="n"/>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-17. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_944125 Чек он-лайн №286598 от 17.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-17. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_944125 Чек он-лайн №286598 от 17.02.2026</t>
         </is>
       </c>
       <c r="D47" s="9" t="n"/>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_226793 Чек он-лайн №933992 от 19.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_226793 Чек он-лайн №933992 от 19.02.2026</t>
         </is>
       </c>
       <c r="D48" s="9" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка MEDTEKHTORG по карте VISA 4274259C13708840 за 2026-02-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_785846 Чек он-лайн №221480 от 20.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф MEDTEKHTORG по карте VISA 4274120034567890 за 2026-02-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_785846 Чек он-лайн №221480 от 20.02.2026</t>
         </is>
       </c>
       <c r="D49" s="9" t="n"/>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_428565 Чек он-лайн №685585 от 20.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_428565 Чек он-лайн №685585 от 20.02.2026</t>
         </is>
       </c>
       <c r="D50" s="9" t="n"/>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-23. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_721666 Чек он-лайн №939379 от 23.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-23. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_721666 Чек он-лайн №939379 от 23.02.2026</t>
         </is>
       </c>
       <c r="D51" s="9" t="n"/>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ONLAYN_MARKET по карте VISA 4274259C13708840 за 2026-02-24. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_794811 Чек он-лайн №478864 от 24.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ONLAYN_MARKET по карте VISA 4274120034567890 за 2026-02-24. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_794811 Чек он-лайн №478864 от 24.02.2026</t>
         </is>
       </c>
       <c r="D52" s="9" t="n"/>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-24. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_956223 Чек он-лайн №605829 от 24.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-24. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_956223 Чек он-лайн №605829 от 24.02.2026</t>
         </is>
       </c>
       <c r="D53" s="9" t="n"/>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-24. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_936713 Чек он-лайн №417166 от 24.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-24. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_936713 Чек он-лайн №417166 от 24.02.2026</t>
         </is>
       </c>
       <c r="D54" s="9" t="n"/>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка WB*ONLAYN_MARKET по карте VISA 4274259C13708840 за 2026-02-25. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_252991 Чек он-лайн №172491 от 25.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф WB*ONLAYN_MARKET по карте VISA 4274120034567890 за 2026-02-25. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_252991 Чек он-лайн №172491 от 25.02.2026</t>
         </is>
       </c>
       <c r="D55" s="9" t="n"/>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-25. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_332288 Чек он-лайн №602125 от 25.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-25. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_332288 Чек он-лайн №602125 от 25.02.2026</t>
         </is>
       </c>
       <c r="D56" s="9" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-02-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_851457 Чек он-лайн №211223 от 27.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-02-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_851457 Чек он-лайн №211223 от 27.02.2026</t>
         </is>
       </c>
       <c r="D57" s="9" t="n"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ OBLAKO_SERVIS по карте VISA 4274259C13708840 за 2026-02-28. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_746603 Чек он-лайн №564134 от 28.02.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ OBLAKO_SERVIS по карте VISA 4274120034567890 за 2026-02-28. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_746603 Чек он-лайн №564134 от 28.02.2026</t>
         </is>
       </c>
       <c r="D58" s="9" t="n"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-03-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_515221 Чек он-лайн №357848 от 02.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-03-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_515221 Чек он-лайн №357848 от 02.03.2026</t>
         </is>
       </c>
       <c r="D59" s="9" t="n"/>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-03-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_449560 Чек он-лайн №543325 от 02.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-03-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_449560 Чек он-лайн №543325 от 02.03.2026</t>
         </is>
       </c>
       <c r="D60" s="9" t="n"/>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка UNIVERSAM_1 по карте VISA 4274259C13708840 за 2026-03-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_413656 Чек он-лайн №967744 от 03.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф UNIVERSAM_1 по карте VISA 4274120034567890 за 2026-03-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_413656 Чек он-лайн №967744 от 03.03.2026</t>
         </is>
       </c>
       <c r="D61" s="9" t="n"/>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274259C13708840 за 2026-03-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_206338 Чек он-лайн №335759 от 03.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274120034567890 за 2026-03-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_206338 Чек он-лайн №335759 от 03.03.2026</t>
         </is>
       </c>
       <c r="D62" s="9" t="n"/>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-03-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_366627 Чек он-лайн №887416 от 03.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-03-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_366627 Чек он-лайн №887416 от 03.03.2026</t>
         </is>
       </c>
       <c r="D63" s="9" t="n"/>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ SPAO STRAP по карте VISA 4274259C13708840 за 2026-03-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_796708 Чек он-лайн №484048 от 05.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ SPAO STRAP по карте VISA 4274120034567890 за 2026-03-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_796708 Чек он-лайн №484048 от 05.03.2026</t>
         </is>
       </c>
       <c r="D64" s="9" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ONLAYN_MARKET по карте VISA 4274259C13708840 за 2026-03-08. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_789643 Чек он-лайн №127005 от 08.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ONLAYN_MARKET по карте VISA 4274120034567890 за 2026-03-08. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_789643 Чек он-лайн №127005 от 08.03.2026</t>
         </is>
       </c>
       <c r="D65" s="9" t="n"/>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-03-10. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_124369 Чек он-лайн №129907 от 10.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-03-10. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_124369 Чек он-лайн №129907 от 10.03.2026</t>
         </is>
       </c>
       <c r="D66" s="9" t="n"/>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-03-10. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_848043 Чек он-лайн №180921 от 10.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-03-10. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_848043 Чек он-лайн №180921 от 10.03.2026</t>
         </is>
       </c>
       <c r="D67" s="9" t="n"/>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-03-11. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_801296 Чек он-лайн №287158 от 11.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-03-11. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_801296 Чек он-лайн №287158 от 11.03.2026</t>
         </is>
       </c>
       <c r="D68" s="9" t="n"/>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка IP SMIRNOV A.V. по карте VISA 4274259C13708840 за 2026-03-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_056615 Чек он-лайн №101764 от 13.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф IP SMIRNOV A.V. по карте VISA 4274120034567890 за 2026-03-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_056615 Чек он-лайн №101764 от 13.03.2026</t>
         </is>
       </c>
       <c r="D69" s="9" t="n"/>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-03-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_910978 Чек он-лайн №337829 от 13.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-03-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_910978 Чек он-лайн №337829 от 13.03.2026</t>
         </is>
       </c>
       <c r="D70" s="9" t="n"/>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка TEHNIKA_MAGAZ по карте VISA 4274259C13708840 за 2026-03-14. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_776571 Чек он-лайн №706115 от 14.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф TEHNIKA_MAGAZ по карте VISA 4274120034567890 за 2026-03-14. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_776571 Чек он-лайн №706115 от 14.03.2026</t>
         </is>
       </c>
       <c r="D71" s="9" t="n"/>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-03-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_749095 Чек он-лайн №701973 от 16.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-03-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_749095 Чек он-лайн №701973 от 16.03.2026</t>
         </is>
       </c>
       <c r="D72" s="9" t="n"/>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ REKLAMA_SERVIS по карте VISA 4274259C13708840 за 2026-03-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1110 КА_902484 Чек он-лайн №357765 от 16.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ REKLAMA_SERVIS по карте VISA 4274120034567890 за 2026-03-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1110 КА_902484 Чек он-лайн №357765 от 16.03.2026</t>
         </is>
       </c>
       <c r="D73" s="9" t="n"/>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274259C13708840 за 2026-03-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_060284 Чек он-лайн №493707 от 16.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274120034567890 за 2026-03-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_060284 Чек он-лайн №493707 от 16.03.2026</t>
         </is>
       </c>
       <c r="D74" s="9" t="n"/>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-03-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_987050 Чек он-лайн №594562 от 19.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-03-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_987050 Чек он-лайн №594562 от 19.03.2026</t>
         </is>
       </c>
       <c r="D75" s="9" t="n"/>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-03-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_159095 Чек он-лайн №561404 от 19.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-03-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_159095 Чек он-лайн №561404 от 19.03.2026</t>
         </is>
       </c>
       <c r="D76" s="9" t="n"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ BANK_PLATFORMA по карте VISA 4274259C13708840 за 2026-03-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_408912 Чек он-лайн №429901 от 20.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ BANK_PLATFORMA по карте VISA 4274120034567890 за 2026-03-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_408912 Чек он-лайн №429901 от 20.03.2026</t>
         </is>
       </c>
       <c r="D77" s="9" t="n"/>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KUZNETSOVA M.A. по карте VISA 4274259C13708840 за 2026-03-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_969504 Чек он-лайн №702612 от 20.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KUZNETSOVA M.A. по карте VISA 4274120034567890 за 2026-03-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_969504 Чек он-лайн №702612 от 20.03.2026</t>
         </is>
       </c>
       <c r="D78" s="9" t="n"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-03-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_898898 Чек он-лайн №782471 от 20.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-03-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_898898 Чек он-лайн №782471 от 20.03.2026</t>
         </is>
       </c>
       <c r="D79" s="9" t="n"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка IP KUZNETSOV A.A. по карте VISA 4274259C13708840 за 2026-03-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_399476 Чек он-лайн №786616 от 20.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф IP KUZNETSOV A.A. по карте VISA 4274120034567890 за 2026-03-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_399476 Чек он-лайн №786616 от 20.03.2026</t>
         </is>
       </c>
       <c r="D80" s="9" t="n"/>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274259C13708840 за 2026-03-23. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_928499 Чек он-лайн №296284 от 23.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274120034567890 за 2026-03-23. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_928499 Чек он-лайн №296284 от 23.03.2026</t>
         </is>
       </c>
       <c r="D81" s="9" t="n"/>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-03-24. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_983007 Чек он-лайн №573275 от 24.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-03-24. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_983007 Чек он-лайн №573275 от 24.03.2026</t>
         </is>
       </c>
       <c r="D82" s="9" t="n"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-03-25. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_746460 Чек он-лайн №834846 от 25.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-03-25. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_746460 Чек он-лайн №834846 от 25.03.2026</t>
         </is>
       </c>
       <c r="D83" s="9" t="n"/>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274259C13708840 за 2026-03-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_191243 Чек он-лайн №703002 от 26.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ZAPRAVKA_YUG по карте VISA 4274120034567890 за 2026-03-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_191243 Чек он-лайн №703002 от 26.03.2026</t>
         </is>
       </c>
       <c r="D84" s="9" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-03-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_568284 Чек он-лайн №844516 от 26.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-03-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_568284 Чек он-лайн №844516 от 26.03.2026</t>
         </is>
       </c>
       <c r="D85" s="9" t="n"/>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка IP MOROZOV G V по карте VISA 4274259C13708840 за 2026-03-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_881754 Чек он-лайн №678075 от 26.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф IP MOROZOV G V по карте VISA 4274120034567890 за 2026-03-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_881754 Чек он-лайн №678075 от 26.03.2026</t>
         </is>
       </c>
       <c r="D86" s="9" t="n"/>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274259C13708840 за 2026-03-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_127704 Чек он-лайн №743998 от 26.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274120034567890 за 2026-03-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_127704 Чек он-лайн №743998 от 26.03.2026</t>
         </is>
       </c>
       <c r="D87" s="9" t="n"/>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка WB*ONLAYN_MARKET по карте VISA 4274259C13708840 за 2026-03-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_914170 Чек он-лайн №962778 от 27.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф WB*ONLAYN_MARKET по карте VISA 4274120034567890 за 2026-03-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_914170 Чек он-лайн №962778 от 27.03.2026</t>
         </is>
       </c>
       <c r="D88" s="9" t="n"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-03-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_189969 Чек он-лайн №695906 от 27.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-03-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_189969 Чек он-лайн №695906 от 27.03.2026</t>
         </is>
       </c>
       <c r="D89" s="9" t="n"/>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-03-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_826851 Чек он-лайн №936115 от 27.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-03-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_826851 Чек он-лайн №936115 от 27.03.2026</t>
         </is>
       </c>
       <c r="D90" s="9" t="n"/>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ OBLAKO_SERVIS по карте VISA 4274259C13708840 за 2026-03-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_837516 Чек он-лайн №181061 от 29.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ OBLAKO_SERVIS по карте VISA 4274120034567890 за 2026-03-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_837516 Чек он-лайн №181061 от 29.03.2026</t>
         </is>
       </c>
       <c r="D91" s="9" t="n"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-03-30. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_458761 Чек он-лайн №231531 от 30.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-03-30. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_458761 Чек он-лайн №231531 от 30.03.2026</t>
         </is>
       </c>
       <c r="D92" s="9" t="n"/>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ IP FEDOROV A Y по карте VISA 4274259C13708840 за 2026-03-30. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_013252 Чек он-лайн №875853 от 30.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ IP FEDOROV A Y по карте VISA 4274120034567890 за 2026-03-30. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_013252 Чек он-лайн №875853 от 30.03.2026</t>
         </is>
       </c>
       <c r="D93" s="9" t="n"/>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ TRANSPORT_LOGISTIK по карте VISA 4274259C13708840 за 2026-03-30. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_394875 Чек он-лайн №509051 от 30.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ TRANSPORT_LOGISTIK по карте VISA 4274120034567890 за 2026-03-30. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_394875 Чек он-лайн №509051 от 30.03.2026</t>
         </is>
       </c>
       <c r="D94" s="9" t="n"/>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_1 по карте VISA 4274259C13708840 за 2026-03-31. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_044120 Чек он-лайн №180607 от 31.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_1 по карте VISA 4274120034567890 за 2026-03-31. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_044120 Чек он-лайн №180607 от 31.03.2026</t>
         </is>
       </c>
       <c r="D95" s="9" t="n"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-03-31. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_623045 Чек он-лайн №386188 от 31.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-03-31. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_623045 Чек он-лайн №386188 от 31.03.2026</t>
         </is>
       </c>
       <c r="D96" s="9" t="n"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-03-31. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_544191 Чек он-лайн №676787 от 31.03.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-03-31. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_544191 Чек он-лайн №676787 от 31.03.2026</t>
         </is>
       </c>
       <c r="D97" s="9" t="n"/>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка UNIVERSAM_2 по карте VISA 4274259C13708840 за 2026-04-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_418787 Чек он-лайн №156231 от 01.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф UNIVERSAM_2 по карте VISA 4274120034567890 за 2026-04-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_418787 Чек он-лайн №156231 от 01.04.2026</t>
         </is>
       </c>
       <c r="D98" s="9" t="n"/>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ONLAYN_MARKET.RU по карте VISA 4274259C13708840 за 2026-04-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_389627 Чек он-лайн №984743 от 01.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ONLAYN_MARKET.RU по карте VISA 4274120034567890 за 2026-04-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_389627 Чек он-лайн №984743 от 01.04.2026</t>
         </is>
       </c>
       <c r="D99" s="9" t="n"/>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274259C13708840 за 2026-04-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_541733 Чек он-лайн №197123 от 01.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274120034567890 за 2026-04-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_541733 Чек он-лайн №197123 от 01.04.2026</t>
         </is>
       </c>
       <c r="D100" s="9" t="n"/>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_705628 Чек он-лайн №827610 от 01.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_705628 Чек он-лайн №827610 от 01.04.2026</t>
         </is>
       </c>
       <c r="D101" s="9" t="n"/>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO STROYINVEST по карте VISA 4274259C13708840 за 2026-04-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_905375 Чек он-лайн №233412 от 01.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO STROYINVEST по карте VISA 4274120034567890 за 2026-04-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_905375 Чек он-лайн №233412 от 01.04.2026</t>
         </is>
       </c>
       <c r="D102" s="9" t="n"/>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_781846 Чек он-лайн №919051 от 01.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_781846 Чек он-лайн №919051 от 01.04.2026</t>
         </is>
       </c>
       <c r="D103" s="9" t="n"/>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KOMPANIYA_TELEKOM по карте VISA 4274259C13708840 за 2026-04-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_401855 Чек он-лайн №139408 от 01.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KOMPANIYA_TELEKOM по карте VISA 4274120034567890 за 2026-04-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_401855 Чек он-лайн №139408 от 01.04.2026</t>
         </is>
       </c>
       <c r="D104" s="9" t="n"/>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO STROYINVEST по карте VISA 4274259C13708840 за 2026-04-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_835783 Чек он-лайн №683183 от 02.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO STROYINVEST по карте VISA 4274120034567890 за 2026-04-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_835783 Чек он-лайн №683183 от 02.04.2026</t>
         </is>
       </c>
       <c r="D105" s="9" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KUZNETSOVA M.A. по карте VISA 4274259C13708840 за 2026-04-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_342720 Чек он-лайн №140776 от 02.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KUZNETSOVA M.A. по карте VISA 4274120034567890 за 2026-04-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_342720 Чек он-лайн №140776 от 02.04.2026</t>
         </is>
       </c>
       <c r="D106" s="9" t="n"/>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка AVTO_MAGAZIN по карте VISA 4274259C13708840 за 2026-04-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_427710 Чек он-лайн №391544 от 02.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф AVTO_MAGAZIN по карте VISA 4274120034567890 за 2026-04-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_427710 Чек он-лайн №391544 от 02.04.2026</t>
         </is>
       </c>
       <c r="D107" s="9" t="n"/>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KUZNETSOVA M.A. по карте VISA 4274259C13708840 за 2026-04-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_317222 Чек он-лайн №583183 от 02.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KUZNETSOVA M.A. по карте VISA 4274120034567890 за 2026-04-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_317222 Чек он-лайн №583183 от 02.04.2026</t>
         </is>
       </c>
       <c r="D108" s="9" t="n"/>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_831631 Чек он-лайн №615753 от 02.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_831631 Чек он-лайн №615753 от 02.04.2026</t>
         </is>
       </c>
       <c r="D109" s="9" t="n"/>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KUZNETSOVA M.A. по карте VISA 4274259C13708840 за 2026-04-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_427683 Чек он-лайн №306255 от 02.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KUZNETSOVA M.A. по карте VISA 4274120034567890 за 2026-04-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_427683 Чек он-лайн №306255 от 02.04.2026</t>
         </is>
       </c>
       <c r="D110" s="9" t="n"/>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка LOGISTIK_TERMINAL по карте VISA 4274259C13708840 за 2026-04-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_031476 Чек он-лайн №878584 от 03.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф LOGISTIK_TERMINAL по карте VISA 4274120034567890 за 2026-04-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_031476 Чек он-лайн №878584 от 03.04.2026</t>
         </is>
       </c>
       <c r="D111" s="9" t="n"/>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO STROYINVEST по карте VISA 4274259C13708840 за 2026-04-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_505058 Чек он-лайн №702215 от 03.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO STROYINVEST по карте VISA 4274120034567890 за 2026-04-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_505058 Чек он-лайн №702215 от 03.04.2026</t>
         </is>
       </c>
       <c r="D112" s="9" t="n"/>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KUZNETSOVA M.A. по карте VISA 4274259C13708840 за 2026-04-04. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_381003 Чек он-лайн №234362 от 04.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KUZNETSOVA M.A. по карте VISA 4274120034567890 за 2026-04-04. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_381003 Чек он-лайн №234362 от 04.04.2026</t>
         </is>
       </c>
       <c r="D113" s="9" t="n"/>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KUZNETSOVA M.A. по карте VISA 4274259C13708840 за 2026-04-04. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_314064 Чек он-лайн №139499 от 04.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KUZNETSOVA M.A. по карте VISA 4274120034567890 за 2026-04-04. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_314064 Чек он-лайн №139499 от 04.04.2026</t>
         </is>
       </c>
       <c r="D114" s="9" t="n"/>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KUZNETSOVA M.A. по карте VISA 4274259C13708840 за 2026-04-04. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_794460 Чек он-лайн №890921 от 04.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KUZNETSOVA M.A. по карте VISA 4274120034567890 за 2026-04-04. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_794460 Чек он-лайн №890921 от 04.04.2026</t>
         </is>
       </c>
       <c r="D115" s="9" t="n"/>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-06. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_148459 Чек он-лайн №904170 от 06.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-06. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_148459 Чек он-лайн №904170 от 06.04.2026</t>
         </is>
       </c>
       <c r="D116" s="9" t="n"/>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-06. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_432974 Чек он-лайн №144672 от 06.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-06. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_432974 Чек он-лайн №144672 от 06.04.2026</t>
         </is>
       </c>
       <c r="D117" s="9" t="n"/>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ONLAYN_MARKET. по карте VISA 4274259C13708840 за 2026-04-06. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_975384 Чек он-лайн №410054 от 06.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ONLAYN_MARKET. по карте VISA 4274120034567890 за 2026-04-06. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_975384 Чек он-лайн №410054 от 06.04.2026</t>
         </is>
       </c>
       <c r="D118" s="9" t="n"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TRANSPORTNAYA по карте VISA 4274259C13708840 за 2026-04-07. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_215940 Чек он-лайн №436892 от 07.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TRANSPORTNAYA по карте VISA 4274120034567890 за 2026-04-07. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_215940 Чек он-лайн №436892 от 07.04.2026</t>
         </is>
       </c>
       <c r="D119" s="9" t="n"/>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ ONLAYN_PLATFORMA по карте VISA 4274259C13708840 за 2026-04-07. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_857328 Чек он-лайн №204401 от 07.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ ONLAYN_PLATFORMA по карте VISA 4274120034567890 за 2026-04-07. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_857328 Чек он-лайн №204401 от 07.04.2026</t>
         </is>
       </c>
       <c r="D120" s="9" t="n"/>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-08. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_288474 Чек он-лайн №830231 от 08.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-08. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_288474 Чек он-лайн №830231 от 08.04.2026</t>
         </is>
       </c>
       <c r="D121" s="9" t="n"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка IP MOROZOV G V по карте VISA 4274259C13708840 за 2026-04-08. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_370190 Чек он-лайн №604607 от 08.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф IP MOROZOV G V по карте VISA 4274120034567890 за 2026-04-08. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_370190 Чек он-лайн №604607 от 08.04.2026</t>
         </is>
       </c>
       <c r="D122" s="9" t="n"/>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_955340 Чек он-лайн №830239 от 09.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_955340 Чек он-лайн №830239 от 09.04.2026</t>
         </is>
       </c>
       <c r="D123" s="9" t="n"/>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="C124" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_649589 Чек он-лайн №984805 от 09.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_649589 Чек он-лайн №984805 от 09.04.2026</t>
         </is>
       </c>
       <c r="D124" s="9" t="n"/>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_064842 Чек он-лайн №283549 от 09.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_064842 Чек он-лайн №283549 от 09.04.2026</t>
         </is>
       </c>
       <c r="D125" s="9" t="n"/>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="C126" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-10. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_735477 Чек он-лайн №790219 от 10.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-10. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_735477 Чек он-лайн №790219 от 10.04.2026</t>
         </is>
       </c>
       <c r="D126" s="9" t="n"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_590650 Чек он-лайн №700651 от 13.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_590650 Чек он-лайн №700651 от 13.04.2026</t>
         </is>
       </c>
       <c r="D127" s="9" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_914989 Чек он-лайн №206336 от 13.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_914989 Чек он-лайн №206336 от 13.04.2026</t>
         </is>
       </c>
       <c r="D128" s="9" t="n"/>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_891395 Чек он-лайн №907688 от 13.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_891395 Чек он-лайн №907688 от 13.04.2026</t>
         </is>
       </c>
       <c r="D129" s="9" t="n"/>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="C130" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-14. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_267815 Чек он-лайн №766293 от 14.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-14. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_267815 Чек он-лайн №766293 от 14.04.2026</t>
         </is>
       </c>
       <c r="D130" s="9" t="n"/>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_1 по карте VISA 4274259C13708840 за 2026-04-15. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_346025 Чек он-лайн №881368 от 15.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_1 по карте VISA 4274120034567890 за 2026-04-15. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_346025 Чек он-лайн №881368 от 15.04.2026</t>
         </is>
       </c>
       <c r="D131" s="9" t="n"/>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="C132" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-15. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_150127 Чек он-лайн №434961 от 15.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-15. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_150127 Чек он-лайн №434961 от 15.04.2026</t>
         </is>
       </c>
       <c r="D132" s="9" t="n"/>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_846930 Чек он-лайн №198593 от 16.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_846930 Чек он-лайн №198593 от 16.04.2026</t>
         </is>
       </c>
       <c r="D133" s="9" t="n"/>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="C134" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KAFE_GOROD по карте VISA 4274259C13708840 за 2026-04-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_548523 Чек он-лайн №174714 от 16.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KAFE_GOROD по карте VISA 4274120034567890 за 2026-04-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_548523 Чек он-лайн №174714 от 16.04.2026</t>
         </is>
       </c>
       <c r="D134" s="9" t="n"/>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_491867 Чек он-лайн №307630 от 16.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_491867 Чек он-лайн №307630 от 16.04.2026</t>
         </is>
       </c>
       <c r="D135" s="9" t="n"/>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="C136" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_DELTA по карте VISA 4274259C13708840 за 2026-04-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_437594 Чек он-лайн №892215 от 16.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_DELTA по карте VISA 4274120034567890 за 2026-04-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_437594 Чек он-лайн №892215 от 16.04.2026</t>
         </is>
       </c>
       <c r="D136" s="9" t="n"/>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_198808 Чек он-лайн №631732 от 16.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_198808 Чек он-лайн №631732 от 16.04.2026</t>
         </is>
       </c>
       <c r="D137" s="9" t="n"/>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="C138" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_DELTA по карте VISA 4274259C13708840 за 2026-04-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_757221 Чек он-лайн №117733 от 19.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_DELTA по карте VISA 4274120034567890 за 2026-04-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_757221 Чек он-лайн №117733 от 19.04.2026</t>
         </is>
       </c>
       <c r="D138" s="9" t="n"/>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка IP SMIRNOV A.V. по карте VISA 4274259C13708840 за 2026-04-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_550927 Чек он-лайн №527396 от 20.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф IP SMIRNOV A.V. по карте VISA 4274120034567890 за 2026-04-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_550927 Чек он-лайн №527396 от 20.04.2026</t>
         </is>
       </c>
       <c r="D139" s="9" t="n"/>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="C140" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_304548 Чек он-лайн №949441 от 20.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_304548 Чек он-лайн №949441 от 20.04.2026</t>
         </is>
       </c>
       <c r="D140" s="9" t="n"/>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_851392 Чек он-лайн №147349 от 20.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_851392 Чек он-лайн №147349 от 20.04.2026</t>
         </is>
       </c>
       <c r="D141" s="9" t="n"/>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="C142" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_208219 Чек он-лайн №295902 от 20.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_208219 Чек он-лайн №295902 от 20.04.2026</t>
         </is>
       </c>
       <c r="D142" s="9" t="n"/>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_516518 Чек он-лайн №963082 от 20.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_516518 Чек он-лайн №963082 от 20.04.2026</t>
         </is>
       </c>
       <c r="D143" s="9" t="n"/>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="C144" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_784087 Чек он-лайн №893304 от 20.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_784087 Чек он-лайн №893304 от 20.04.2026</t>
         </is>
       </c>
       <c r="D144" s="9" t="n"/>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-21. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_870915 Чек он-лайн №319271 от 21.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-21. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_870915 Чек он-лайн №319271 от 21.04.2026</t>
         </is>
       </c>
       <c r="D145" s="9" t="n"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="C146" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка IP SMIRNOV A.V. по карте VISA 4274259C13708840 за 2026-04-21. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_393253 Чек он-лайн №982699 от 21.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф IP SMIRNOV A.V. по карте VISA 4274120034567890 за 2026-04-21. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_393253 Чек он-лайн №982699 от 21.04.2026</t>
         </is>
       </c>
       <c r="D146" s="9" t="n"/>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ZAPRAVKA_SEVER по карте VISA 4274259C13708840 за 2026-04-21. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_002990 Чек он-лайн №426833 от 21.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ZAPRAVKA_SEVER по карте VISA 4274120034567890 за 2026-04-21. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_002990 Чек он-лайн №426833 от 21.04.2026</t>
         </is>
       </c>
       <c r="D147" s="9" t="n"/>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="C148" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_673005 Чек он-лайн №241776 от 22.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_673005 Чек он-лайн №241776 от 22.04.2026</t>
         </is>
       </c>
       <c r="D148" s="9" t="n"/>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_900958 Чек он-лайн №520187 от 22.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_900958 Чек он-лайн №520187 от 22.04.2026</t>
         </is>
       </c>
       <c r="D149" s="9" t="n"/>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="C150" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка PROFESSIONAL. по карте VISA 4274259C13708840 за 2026-04-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_329152 Чек он-лайн №688745 от 22.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф PROFESSIONAL. по карте VISA 4274120034567890 за 2026-04-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_329152 Чек он-лайн №688745 от 22.04.2026</t>
         </is>
       </c>
       <c r="D150" s="9" t="n"/>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_2 по карте VISA 4274259C13708840 за 2026-04-23. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_002990 Чек он-лайн №587127 от 23.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_2 по карте VISA 4274120034567890 за 2026-04-23. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_002990 Чек он-лайн №587127 от 23.04.2026</t>
         </is>
       </c>
       <c r="D151" s="9" t="n"/>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="C152" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ONLAYN_MARKET. по карте VISA 4274259C13708840 за 2026-04-23. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_618229 Чек он-лайн №809555 от 23.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ONLAYN_MARKET. по карте VISA 4274120034567890 за 2026-04-23. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_618229 Чек он-лайн №809555 от 23.04.2026</t>
         </is>
       </c>
       <c r="D152" s="9" t="n"/>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-23. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_649323 Чек он-лайн №204056 от 23.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-23. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_649323 Чек он-лайн №204056 от 23.04.2026</t>
         </is>
       </c>
       <c r="D153" s="9" t="n"/>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="C154" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ONLAYN_MARKET по карте VISA 4274259C13708840 за 2026-04-23. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_313496 Чек он-лайн №731673 от 23.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ONLAYN_MARKET по карте VISA 4274120034567890 за 2026-04-23. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_313496 Чек он-лайн №731673 от 23.04.2026</t>
         </is>
       </c>
       <c r="D154" s="9" t="n"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-24. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_394202 Чек он-лайн №690753 от 24.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-24. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_394202 Чек он-лайн №690753 от 24.04.2026</t>
         </is>
       </c>
       <c r="D155" s="9" t="n"/>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C156" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO STROYINVEST по карте VISA 4274259C13708840 за 2026-04-25. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_746429 Чек он-лайн №824134 от 25.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO STROYINVEST по карте VISA 4274120034567890 за 2026-04-25. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_746429 Чек он-лайн №824134 от 25.04.2026</t>
         </is>
       </c>
       <c r="D156" s="9" t="n"/>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO STROYINVEST по карте VISA 4274259C13708840 за 2026-04-25. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_116181 Чек он-лайн №390744 от 25.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO STROYINVEST по карте VISA 4274120034567890 за 2026-04-25. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_116181 Чек он-лайн №390744 от 25.04.2026</t>
         </is>
       </c>
       <c r="D157" s="9" t="n"/>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="C158" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка WB*ONLAYN_MARKET по карте VISA 4274259C13708840 за 2026-04-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_420169 Чек он-лайн №258056 от 26.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф WB*ONLAYN_MARKET по карте VISA 4274120034567890 за 2026-04-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_420169 Чек он-лайн №258056 от 26.04.2026</t>
         </is>
       </c>
       <c r="D158" s="9" t="n"/>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_857529 Чек он-лайн №849390 от 26.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_857529 Чек он-лайн №849390 от 26.04.2026</t>
         </is>
       </c>
       <c r="D159" s="9" t="n"/>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="C160" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ FINANCE_PLUS LLC по карте VISA 4274259C13708840 за 2026-04-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_335472 Чек он-лайн №646625 от 27.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ FINANCE_PLUS LLC по карте VISA 4274120034567890 за 2026-04-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_335472 Чек он-лайн №646625 от 27.04.2026</t>
         </is>
       </c>
       <c r="D160" s="9" t="n"/>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_252885 Чек он-лайн №446256 от 27.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_252885 Чек он-лайн №446256 от 27.04.2026</t>
         </is>
       </c>
       <c r="D161" s="9" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="C162" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-28. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_186814 Чек он-лайн №430764 от 28.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-28. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_186814 Чек он-лайн №430764 от 28.04.2026</t>
         </is>
       </c>
       <c r="D162" s="9" t="n"/>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-28. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_801897 Чек он-лайн №774083 от 28.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-28. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_801897 Чек он-лайн №774083 от 28.04.2026</t>
         </is>
       </c>
       <c r="D163" s="9" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="C164" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка VK*OBLAKO_SERVIS по карте VISA 4274259C13708840 за 2026-04-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_436573 Чек он-лайн №705498 от 29.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф VK*OBLAKO_SERVIS по карте VISA 4274120034567890 за 2026-04-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_436573 Чек он-лайн №705498 от 29.04.2026</t>
         </is>
       </c>
       <c r="D164" s="9" t="n"/>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_815942 Чек он-лайн №301473 от 29.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_815942 Чек он-лайн №301473 от 29.04.2026</t>
         </is>
       </c>
       <c r="D165" s="9" t="n"/>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C166" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_805652 Чек он-лайн №831830 от 29.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_805652 Чек он-лайн №831830 от 29.04.2026</t>
         </is>
       </c>
       <c r="D166" s="9" t="n"/>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-04-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_577237 Чек он-лайн №980540 от 29.04.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-04-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_577237 Чек он-лайн №980540 от 29.04.2026</t>
         </is>
       </c>
       <c r="D167" s="9" t="n"/>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="C168" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_867380 Чек он-лайн №554524 от 01.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_867380 Чек он-лайн №554524 от 01.05.2026</t>
         </is>
       </c>
       <c r="D168" s="9" t="n"/>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_785199 Чек он-лайн №544707 от 01.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_785199 Чек он-лайн №544707 от 01.05.2026</t>
         </is>
       </c>
       <c r="D169" s="9" t="n"/>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="C170" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_511617 Чек он-лайн №320660 от 02.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_511617 Чек он-лайн №320660 от 02.05.2026</t>
         </is>
       </c>
       <c r="D170" s="9" t="n"/>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_412085 Чек он-лайн №183729 от 02.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_412085 Чек он-лайн №183729 от 02.05.2026</t>
         </is>
       </c>
       <c r="D171" s="9" t="n"/>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="C172" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO STROYINVEST по карте VISA 4274259C13708840 за 2026-05-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_215979 Чек он-лайн №808311 от 03.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO STROYINVEST по карте VISA 4274120034567890 за 2026-05-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_215979 Чек он-лайн №808311 от 03.05.2026</t>
         </is>
       </c>
       <c r="D172" s="9" t="n"/>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-04. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_086300 Чек он-лайн №401784 от 04.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-04. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_086300 Чек он-лайн №401784 от 04.05.2026</t>
         </is>
       </c>
       <c r="D173" s="9" t="n"/>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="C174" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-04. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_059699 Чек он-лайн №546297 от 04.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-04. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_059699 Чек он-лайн №546297 от 04.05.2026</t>
         </is>
       </c>
       <c r="D174" s="9" t="n"/>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_877054 Чек он-лайн №779212 от 05.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_877054 Чек он-лайн №779212 от 05.05.2026</t>
         </is>
       </c>
       <c r="D175" s="9" t="n"/>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="C176" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_1 по карте VISA 4274259C13708840 за 2026-05-06. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_631810 Чек он-лайн №824868 от 06.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_1 по карте VISA 4274120034567890 за 2026-05-06. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_631810 Чек он-лайн №824868 от 06.05.2026</t>
         </is>
       </c>
       <c r="D176" s="9" t="n"/>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ZAPRAVKA_SEVER по карте VISA 4274259C13708840 за 2026-05-07. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_723117 Чек он-лайн №319478 от 07.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ZAPRAVKA_SEVER по карте VISA 4274120034567890 за 2026-05-07. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_723117 Чек он-лайн №319478 от 07.05.2026</t>
         </is>
       </c>
       <c r="D177" s="9" t="n"/>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C178" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ZAPRAVKA_SEVER по карте VISA 4274259C13708840 за 2026-05-07. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_775717 Чек он-лайн №595767 от 07.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ZAPRAVKA_SEVER по карте VISA 4274120034567890 за 2026-05-07. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_775717 Чек он-лайн №595767 от 07.05.2026</t>
         </is>
       </c>
       <c r="D178" s="9" t="n"/>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-07. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_818691 Чек он-лайн №342784 от 07.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-07. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_818691 Чек он-лайн №342784 от 07.05.2026</t>
         </is>
       </c>
       <c r="D179" s="9" t="n"/>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="C180" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-08. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_512572 Чек он-лайн №816498 от 08.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-08. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_512572 Чек он-лайн №816498 от 08.05.2026</t>
         </is>
       </c>
       <c r="D180" s="9" t="n"/>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-10. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_875320 Чек он-лайн №109542 от 10.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-10. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_875320 Чек он-лайн №109542 от 10.05.2026</t>
         </is>
       </c>
       <c r="D181" s="9" t="n"/>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C182" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-10. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_409307 Чек он-лайн №144139 от 10.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-10. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_409307 Чек он-лайн №144139 от 10.05.2026</t>
         </is>
       </c>
       <c r="D182" s="9" t="n"/>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-12. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_894314 Чек он-лайн №421350 от 12.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-12. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_894314 Чек он-лайн №421350 от 12.05.2026</t>
         </is>
       </c>
       <c r="D183" s="9" t="n"/>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="C184" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ZAPRAVKA_SEVER по карте VISA 4274259C13708840 за 2026-05-12. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_101566 Чек он-лайн №630701 от 12.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ZAPRAVKA_SEVER по карте VISA 4274120034567890 за 2026-05-12. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_101566 Чек он-лайн №630701 от 12.05.2026</t>
         </is>
       </c>
       <c r="D184" s="9" t="n"/>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_651730 Чек он-лайн №427440 от 13.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_651730 Чек он-лайн №427440 от 13.05.2026</t>
         </is>
       </c>
       <c r="D185" s="9" t="n"/>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C186" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_750317 Чек он-лайн №855181 от 13.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_750317 Чек он-лайн №855181 от 13.05.2026</t>
         </is>
       </c>
       <c r="D186" s="9" t="n"/>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_477321 Чек он-лайн №879797 от 13.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_477321 Чек он-лайн №879797 от 13.05.2026</t>
         </is>
       </c>
       <c r="D187" s="9" t="n"/>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="C188" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка IP MOROZOV G V по карте VISA 4274259C13708840 за 2026-05-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_631066 Чек он-лайн №756298 от 13.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф IP MOROZOV G V по карте VISA 4274120034567890 за 2026-05-13. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_631066 Чек он-лайн №756298 от 13.05.2026</t>
         </is>
       </c>
       <c r="D188" s="9" t="n"/>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-14. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_246032 Чек он-лайн №664663 от 14.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-14. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_246032 Чек он-лайн №664663 от 14.05.2026</t>
         </is>
       </c>
       <c r="D189" s="9" t="n"/>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="C190" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ONLAYN_MARKET. по карте VISA 4274259C13708840 за 2026-05-15. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_186871 Чек он-лайн №389333 от 15.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ONLAYN_MARKET. по карте VISA 4274120034567890 за 2026-05-15. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_186871 Чек он-лайн №389333 от 15.05.2026</t>
         </is>
       </c>
       <c r="D190" s="9" t="n"/>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-15. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_983519 Чек он-лайн №957766 от 15.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-15. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_983519 Чек он-лайн №957766 от 15.05.2026</t>
         </is>
       </c>
       <c r="D191" s="9" t="n"/>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="C192" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ONLAYN_MARKET. по карте VISA 4274259C13708840 за 2026-05-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_661760 Чек он-лайн №384559 от 16.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ONLAYN_MARKET. по карте VISA 4274120034567890 за 2026-05-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_661760 Чек он-лайн №384559 от 16.05.2026</t>
         </is>
       </c>
       <c r="D192" s="9" t="n"/>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ONLAYN_MARKET. по карте VISA 4274259C13708840 за 2026-05-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_204590 Чек он-лайн №574575 от 16.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ONLAYN_MARKET. по карте VISA 4274120034567890 за 2026-05-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_204590 Чек он-лайн №574575 от 16.05.2026</t>
         </is>
       </c>
       <c r="D193" s="9" t="n"/>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KUZNETSOVA M.A. по карте VISA 4274259C13708840 за 2026-05-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_812419 Чек он-лайн №353545 от 16.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KUZNETSOVA M.A. по карте VISA 4274120034567890 за 2026-05-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_812419 Чек он-лайн №353545 от 16.05.2026</t>
         </is>
       </c>
       <c r="D194" s="9" t="n"/>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ IP FEDOROV A Y по карте VISA 4274259C13708840 за 2026-05-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_342646 Чек он-лайн №498469 от 16.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ IP FEDOROV A Y по карте VISA 4274120034567890 за 2026-05-16. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_342646 Чек он-лайн №498469 от 16.05.2026</t>
         </is>
       </c>
       <c r="D195" s="9" t="n"/>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ FINANCE_PLUS LLC по карте VISA 4274259C13708840 за 2026-05-17. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_539225 Чек он-лайн №301528 от 17.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ FINANCE_PLUS LLC по карте VISA 4274120034567890 за 2026-05-17. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_539225 Чек он-лайн №301528 от 17.05.2026</t>
         </is>
       </c>
       <c r="D196" s="9" t="n"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-18. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_869976 Чек он-лайн №396646 от 18.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-18. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_869976 Чек он-лайн №396646 от 18.05.2026</t>
         </is>
       </c>
       <c r="D197" s="9" t="n"/>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="C198" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-18. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_740610 Чек он-лайн №844659 от 18.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-18. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_740610 Чек он-лайн №844659 от 18.05.2026</t>
         </is>
       </c>
       <c r="D198" s="9" t="n"/>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_123660 Чек он-лайн №182678 от 19.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_123660 Чек он-лайн №182678 от 19.05.2026</t>
         </is>
       </c>
       <c r="D199" s="9" t="n"/>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="C200" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_979086 Чек он-лайн №477206 от 19.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_979086 Чек он-лайн №477206 от 19.05.2026</t>
         </is>
       </c>
       <c r="D200" s="9" t="n"/>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_458908 Чек он-лайн №160887 от 19.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-19. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_458908 Чек он-лайн №160887 от 19.05.2026</t>
         </is>
       </c>
       <c r="D201" s="9" t="n"/>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C202" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_840263 Чек он-лайн №546434 от 20.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-20. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_840263 Чек он-лайн №546434 от 20.05.2026</t>
         </is>
       </c>
       <c r="D202" s="9" t="n"/>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-21. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_807218 Чек он-лайн №216264 от 21.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-21. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_807218 Чек он-лайн №216264 от 21.05.2026</t>
         </is>
       </c>
       <c r="D203" s="9" t="n"/>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C204" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_3 по карте VISA 4274259C13708840 за 2026-05-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_479571 Чек он-лайн №175997 от 22.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_3 по карте VISA 4274120034567890 за 2026-05-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_479571 Чек он-лайн №175997 от 22.05.2026</t>
         </is>
       </c>
       <c r="D204" s="9" t="n"/>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ONLAYN_MARKET. по карте VISA 4274259C13708840 за 2026-05-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_915200 Чек он-лайн №554793 от 22.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ONLAYN_MARKET. по карте VISA 4274120034567890 за 2026-05-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_915200 Чек он-лайн №554793 от 22.05.2026</t>
         </is>
       </c>
       <c r="D205" s="9" t="n"/>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="C206" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_ALFA по карте VISA 4274259C13708840 за 2026-05-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_559646 Чек он-лайн №989510 от 22.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_ALFA по карте VISA 4274120034567890 за 2026-05-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_559646 Чек он-лайн №989510 от 22.05.2026</t>
         </is>
       </c>
       <c r="D206" s="9" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_477653 Чек он-лайн №901167 от 22.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_477653 Чек он-лайн №901167 от 22.05.2026</t>
         </is>
       </c>
       <c r="D207" s="9" t="n"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C208" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ONLAYN_MARKET. по карте VISA 4274259C13708840 за 2026-05-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_955748 Чек он-лайн №590599 от 22.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ONLAYN_MARKET. по карте VISA 4274120034567890 за 2026-05-22. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_955748 Чек он-лайн №590599 от 22.05.2026</t>
         </is>
       </c>
       <c r="D208" s="9" t="n"/>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ZAPRAVKA_SEVER по карте VISA 4274259C13708840 за 2026-05-25. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_250531 Чек он-лайн №302661 от 25.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ZAPRAVKA_SEVER по карте VISA 4274120034567890 за 2026-05-25. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_250531 Чек он-лайн №302661 от 25.05.2026</t>
         </is>
       </c>
       <c r="D209" s="9" t="n"/>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="C210" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка WB*ONLAYN_MARKET по карте VISA 4274259C13708840 за 2026-05-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_923739 Чек он-лайн №334570 от 26.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф WB*ONLAYN_MARKET по карте VISA 4274120034567890 за 2026-05-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_923739 Чек он-лайн №334570 от 26.05.2026</t>
         </is>
       </c>
       <c r="D210" s="9" t="n"/>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_1 по карте VISA 4274259C13708840 за 2026-05-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_467241 Чек он-лайн №347925 от 26.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_1 по карте VISA 4274120034567890 за 2026-05-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_467241 Чек он-лайн №347925 от 26.05.2026</t>
         </is>
       </c>
       <c r="D211" s="9" t="n"/>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="C212" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_1 по карте VISA 4274259C13708840 за 2026-05-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_157168 Чек он-лайн №206924 от 26.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ POCHTA_SERVIS_1 по карте VISA 4274120034567890 за 2026-05-26. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_157168 Чек он-лайн №206924 от 26.05.2026</t>
         </is>
       </c>
       <c r="D212" s="9" t="n"/>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_469948 Чек он-лайн №899325 от 27.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_469948 Чек он-лайн №899325 от 27.05.2026</t>
         </is>
       </c>
       <c r="D213" s="9" t="n"/>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="C214" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_186017 Чек он-лайн №354888 от 27.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-27. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_186017 Чек он-лайн №354888 от 27.05.2026</t>
         </is>
       </c>
       <c r="D214" s="9" t="n"/>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="C215" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-28. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_482466 Чек он-лайн №752706 от 28.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-28. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_482466 Чек он-лайн №752706 от 28.05.2026</t>
         </is>
       </c>
       <c r="D215" s="9" t="n"/>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="C216" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ONLAYN_MARKET по карте VISA 4274259C13708840 за 2026-05-28. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_661908 Чек он-лайн №277280 от 28.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ONLAYN_MARKET по карте VISA 4274120034567890 за 2026-05-28. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_661908 Чек он-лайн №277280 от 28.05.2026</t>
         </is>
       </c>
       <c r="D216" s="9" t="n"/>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="C217" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка VK*OBLAKO_SERVIS по карте VISA 4274259C13708840 за 2026-05-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_578633 Чек он-лайн №232464 от 29.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф VK*OBLAKO_SERVIS по карте VISA 4274120034567890 за 2026-05-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1010 КА_578633 Чек он-лайн №232464 от 29.05.2026</t>
         </is>
       </c>
       <c r="D217" s="9" t="n"/>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="C218" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_DELTA по карте VISA 4274259C13708840 за 2026-05-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_210308 Чек он-лайн №305979 от 29.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_DELTA по карте VISA 4274120034567890 за 2026-05-29. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_210308 Чек он-лайн №305979 от 29.05.2026</t>
         </is>
       </c>
       <c r="D218" s="9" t="n"/>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-05-30. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_476988 Чек он-лайн №369052 от 30.05.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-05-30. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_476988 Чек он-лайн №369052 от 30.05.2026</t>
         </is>
       </c>
       <c r="D219" s="9" t="n"/>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="C220" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-06-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_655963 Чек он-лайн №884814 от 01.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-06-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_655963 Чек он-лайн №884814 от 01.06.2026</t>
         </is>
       </c>
       <c r="D220" s="9" t="n"/>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка ENERGO_SERVIS по карте VISA 4274259C13708840 за 2026-06-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_333658 Чек он-лайн №501619 от 01.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф ENERGO_SERVIS по карте VISA 4274120034567890 за 2026-06-01. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_333658 Чек он-лайн №501619 от 01.06.2026</t>
         </is>
       </c>
       <c r="D221" s="9" t="n"/>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C222" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-06-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_445615 Чек он-лайн №279251 от 02.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-06-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_445615 Чек он-лайн №279251 от 02.06.2026</t>
         </is>
       </c>
       <c r="D222" s="9" t="n"/>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-06-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_767893 Чек он-лайн №711391 от 02.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-06-02. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_767893 Чек он-лайн №711391 от 02.06.2026</t>
         </is>
       </c>
       <c r="D223" s="9" t="n"/>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="C224" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-06-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_443509 Чек он-лайн №496845 от 03.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-06-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_443509 Чек он-лайн №496845 от 03.06.2026</t>
         </is>
       </c>
       <c r="D224" s="9" t="n"/>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KUZNETSOVA M.A. по карте VISA 4274259C13708840 за 2026-06-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_349127 Чек он-лайн №525419 от 03.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KUZNETSOVA M.A. по карте VISA 4274120034567890 за 2026-06-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_349127 Чек он-лайн №525419 от 03.06.2026</t>
         </is>
       </c>
       <c r="D225" s="9" t="n"/>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C226" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-06-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_583519 Чек он-лайн №521381 от 03.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-06-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_583519 Чек он-лайн №521381 от 03.06.2026</t>
         </is>
       </c>
       <c r="D226" s="9" t="n"/>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KUZNETSOVA M.A. по карте VISA 4274259C13708840 за 2026-06-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_161718 Чек он-лайн №164020 от 03.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KUZNETSOVA M.A. по карте VISA 4274120034567890 за 2026-06-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_161718 Чек он-лайн №164020 от 03.06.2026</t>
         </is>
       </c>
       <c r="D227" s="9" t="n"/>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="C228" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KUZNETSOVA M.A. по карте VISA 4274259C13708840 за 2026-06-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_790806 Чек он-лайн №361003 от 03.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KUZNETSOVA M.A. по карте VISA 4274120034567890 за 2026-06-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_790806 Чек он-лайн №361003 от 03.06.2026</t>
         </is>
       </c>
       <c r="D228" s="9" t="n"/>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KUZNETSOVA M.A. по карте VISA 4274259C13708840 за 2026-06-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_606221 Чек он-лайн №155976 от 03.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KUZNETSOVA M.A. по карте VISA 4274120034567890 за 2026-06-03. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_606221 Чек он-лайн №155976 от 03.06.2026</t>
         </is>
       </c>
       <c r="D229" s="9" t="n"/>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="C230" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка MAGAZIN_MAYAK по карте VISA 4274259C13708840 за 2026-06-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_524385 Чек он-лайн №889948 от 05.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф MAGAZIN_MAYAK по карте VISA 4274120034567890 за 2026-06-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_524385 Чек он-лайн №889948 от 05.06.2026</t>
         </is>
       </c>
       <c r="D230" s="9" t="n"/>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-06-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_318929 Чек он-лайн №116491 от 05.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-06-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_318929 Чек он-лайн №116491 от 05.06.2026</t>
         </is>
       </c>
       <c r="D231" s="9" t="n"/>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="C232" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-06-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_493679 Чек он-лайн №189229 от 05.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-06-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_493679 Чек он-лайн №189229 от 05.06.2026</t>
         </is>
       </c>
       <c r="D232" s="9" t="n"/>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="C233" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-06-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_185835 Чек он-лайн №968178 от 05.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-06-05. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_185835 Чек он-лайн №968178 от 05.06.2026</t>
         </is>
       </c>
       <c r="D233" s="9" t="n"/>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C234" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_GAMMA по карте VISA 4274259C13708840 за 2026-06-06. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_253471 Чек он-лайн №420596 от 06.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ MAGAZIN_GAMMA по карте VISA 4274120034567890 за 2026-06-06. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_253471 Чек он-лайн №420596 от 06.06.2026</t>
         </is>
       </c>
       <c r="D234" s="9" t="n"/>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274259C13708840 за 2026-06-06. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_881649 Чек он-лайн №685342 от 06.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ STROYMATERIAL по карте VISA 4274120034567890 за 2026-06-06. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1410 КА_881649 Чек он-лайн №685342 от 06.06.2026</t>
         </is>
       </c>
       <c r="D235" s="9" t="n"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="C236" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка KUZNETSOVA M.A. по карте VISA 4274259C13708840 за 2026-06-08. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_988865 Чек он-лайн №958554 от 08.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф KUZNETSOVA M.A. по карте VISA 4274120034567890 за 2026-06-08. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_988865 Чек он-лайн №958554 от 08.06.2026</t>
         </is>
       </c>
       <c r="D236" s="9" t="n"/>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-06-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_767063 Чек он-лайн №874997 от 09.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-06-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_767063 Чек он-лайн №874997 от 09.06.2026</t>
         </is>
       </c>
       <c r="D237" s="9" t="n"/>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="C238" s="12" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-06-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_608472 Чек он-лайн №136101 от 09.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-06-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_608472 Чек он-лайн №136101 от 09.06.2026</t>
         </is>
       </c>
       <c r="D238" s="9" t="n"/>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="C239" s="16" t="inlineStr">
         <is>
-          <t>Покупка PURCHASE_CB в ТУ Сбербанка OOO TEHNOPROM по карте VISA 4274259C13708840 за 2026-06-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_513290 Чек он-лайн №742914 от 09.06.2026</t>
+          <t>Покупка PURCHASE_CB в ТУ Банка Триумф OOO TEHNOPROM по карте VISA 4274120034567890 за 2026-06-09. Держатель ИВАНОВ ПЁТР АЛЕКСЕЕВИЧ. 1310 КА_513290 Чек он-лайн №742914 от 09.06.2026</t>
         </is>
       </c>
       <c r="D239" s="9" t="n"/>
